--- a/extenbooks/ES1001.xlsx
+++ b/extenbooks/ES1001.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -772,7 +772,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 1</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952–1980</t>
+          <t>1952-1980</t>
         </is>
       </c>
     </row>
@@ -874,174 +874,175 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1001-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tonak 1984 PhD Dissertation</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1001 — Labor Share of National Taxes (Tonak 1984)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: External study (Tonak 1984 PhD Dissertation)</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t># ES1001 — Labor Share of National Taxes (Tonak 1984)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Period**: [1952, 1980]</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Units**: share</t>
+          <t>**Chapter**: External study (Tonak 1984 PhD Dissertation)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Period**: [1952, 1980]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Units**: share</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Total taxes paid by labor, per Tonak's PhD dissertation Table V. Read directly from the digitized Table V; column `labor_taxes`. Endpoints: 1952=34.58B, 1980=456.39B.</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Source</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Total taxes paid by labor, per Tonak's PhD dissertation Table V. Read directly from the digitized Table V; column `labor_taxes`. Endpoints: 1952=34.58B, 1980=456.39B.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>`data/source/external_studies/Tonak1984_table_V_taxes_labor_nonlabor_1952_1980.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_ES1001_labor_share_tonak1984.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_ES1001_labor_share_tonak1984.py`.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>## Validation</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>`data/source/external_studies/Tonak1984_table_V_taxes_labor_nonlabor_1952_1980.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_ES1001_labor_share_tonak1984.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_ES1001_labor_share_tonak1984.py`.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>V03 PASS against endpoint values verified directly against the source CSV.</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>## Validation</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>## Provenance</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>V03 PASS against endpoint values verified directly against the source CSV.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>data/source/external_studies/Tonak1984_table_V_taxes_labor_nonlabor_1952_1980.csv</t>
+          <t>## Provenance</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -&gt; L01_ES1001 -&gt; data/intermediate/ES1001.csv</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; P02_ES1001 -&gt; data/final/ES1001.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1050,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; V03_ES1001 -&gt; data/intermediate/validation/ES1001.json</t>
+          <t>data/source/external_studies/Tonak1984_table_V_taxes_labor_nonlabor_1952_1980.csv</t>
         </is>
       </c>
     </row>
@@ -1057,53 +1058,77 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  -&gt; L01_ES1001 -&gt; data/intermediate/ES1001.csv</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -&gt; P02_ES1001 -&gt; data/final/ES1001.csv</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t xml:space="preserve">  -&gt; V03_ES1001 -&gt; data/intermediate/validation/ES1001.json</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Tonak, E. Ahmet. 1984. 'A Conceptualization of State Revenues and Expenditures: The U.S., 1952-1980.' PhD dissertation, New School for Social Research.</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>## Citation</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Tonak, E. Ahmet. 1984. 'A Conceptualization of State Revenues and Expenditures: The U.S., 1952-1980.' PhD dissertation, New School for Social Research.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
         </is>
@@ -1120,10 +1145,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1148,267 +1173,423 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Labor share (W/NI) is computed as the ratio of wages and salaries received by workers to national income. Tonak allocates NIPA employee compensation between labor and non-labor using an income-proportional 'labor share' factor (Total labor income / Personal income). For 1964 this factor is 0.73. The resulting series covers 1952-1980 and appears in Chapter IV, Table II ('Calculation of Labor Share, 1952-80'). The labor share is also used as the allocation key for Group II taxes and Group II expenditures throughout the dissertation.</t>
+          <t>Direct verbatim definition of labor share from Tonak 1984 Chapter IV (chunk_11, page 90): defines the canonical formula LS = Total Labor Income / Adjusted Personal Income, where Adjusted Personal Income = Personal Income - Imputed Income. This is the exact methodology ES1001 must implement.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables, Chapter IV Table II, p.92); chunk_001/full_transcription.md (Abstract, Table of Contents)</t>
+          <t>Tonak 1984, Chapter IV, p.90 (HDARP chunk_11)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Primary source: Tonak (1984) PhD Dissertation, New School for Social Research, Chapter IV Table II ('Calculation of Labor Share, 1952-80', p.92), covering 1952-1980 (28 annual observations). Underlying raw data from U.S. National Income and Product Accounts (NIPA). Table III ('Comparison of Labor Shares — Weisskopf and Tonak', p.93) provides cross-validation against Weisskopf's estimates. Per DEC-012, the data_quality must be 'real_extracted' — values must be taken from HDARP-extracted Table II, not synthetically generated.</t>
+          <t>Tonak 1984 Table II structure and values range verbatim from chunk_11 (p.92): confirms 5-column structure, 1952-1980 annual coverage, labor share range .71-.75 (typical .72-.73), and NIPA source line references. This is the primary source the ES1001 chopped CSV must populate from.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables p.v, Chapter IV Table II p.92, Table III p.93)</t>
+          <t>Tonak 1984, Chapter IV, Table II, p.92 (HDARP chunk_11)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>table_identification</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The primary table is Chapter IV Table II: 'Calculation of Labor Share, 1952-80' (p.92). A comparison table, Chapter IV Table III: 'Comparison of Labor Shares — Weisskopf and Tonak' (p.93), provides external validation. The labor share formula is also referenced in Chapter IV Table IV: 'Labor and Non-Labor Portions of Total Taxes — Selected Years' (p.95) and Table V: 'Labor and Non-Labor Portions of Total Taxes' (p.98). These tables are located in later HDARP chunks (not yet extracted in chunks 001-002).</t>
+          <t>Worked 1980 example from Tonak 1984 labor_share_formula equation extraction (chunk_11): provides exact numerical benchmark (LS = 0.71 for 1980) for V03 validator of ES1001. The values (TLI=1483.370, PI=2160.401, II=59.299) anchor the chopped CSV's terminal-year value.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables pp.v-vi)</t>
+          <t>Tonak 1984, Chapter IV, Table II equation extraction (HDARP chunk_11)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Labor Share = Total labor income / Personal income. This ratio is applied to allocate Group II government expenditures and Group II personal taxes between workers and non-workers. Example value for 1964: 0.73 (cited in the 1987 Shaikh-Tonak paper's Appendix Table 1 footnote b).</t>
+          <t>Weisskopf cross-validation passage from Tonak 1984 Chapter IV (chunk_11, p.91): documents the methodological divergence between Tonak's labor share and Weisskopf's IRS-derived measure, and Tonak's own assessment that his estimate is conservative (no overestimation). This supports the ES1001 caveat that this series differs from mainstream labor share measures.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1984_Tonak_State_Revenues/chunk_001/full_transcription.md (Abstract); 1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Appendix Table 1 footnote b)</t>
+          <t>Tonak 1984, Chapter IV, p.91 (HDARP chunk_11)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Per DEC-012 (No Synthetic Data Policy, 2026-05-03): ES1001 was previously identified as using synthetic data generated from summary statistics. The annual Table II values have not yet been extracted from the later HDARP chunks of Tonak (1984). Until a full HDARP extraction of Chapter IV (chunks covering pp.88-98) is completed, this series must be marked data_unavailable with an empty CSV. No np.random or benchmark-interpolation fills are permitted.</t>
+          <t>To obtain the portions of these expenditures directed towards labor, all of the items in this group are multiplied by the "labor share" (0.73 for 1964) except the item of Transportation which is also adjusted by the "Gas Share of Passenger Cars" (Tonak 1984:Chap. IV; Appendix II).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md#DEC-012</t>
+          <t>Shaikh &amp; Tonak 1987, Appendix Table 1 footnote b, p.191</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The labor share concept in Tonak (1984) is defined as wages/national income following the labor theory of value framework, which differs from conventional national accounts definitions (e.g., BLS or BEA labor share). Tonak explicitly compares with Weisskopf's estimates (Chapter IV Table III, p.93), documenting methodological divergence. Users must not conflate this series with mainstream labor share measures.</t>
+          <t>Workers' share = (Total labor income / Personal income) × Group II total</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables, Chapter IV Table III p.93)</t>
+          <t>Shaikh &amp; Tonak 1987, Empirical Methodology, p.186</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cross_study_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The 1987 Shaikh-Tonak paper uses the same labor share methodology (citing 'Tonak 1984:Chap. IV; 1987') to allocate Group II expenditures and taxes. The 1964 labor share of 0.73 is directly confirmed in S&amp;T (1987) Appendix Table 1 footnote b. The labor share for ES1001 is therefore fully consistent with the ES1101/ES1102/ES1103 series from the 1987 paper.</t>
+          <t>For rationale and procedures of "labor share method," see Tonak (1984: Chap. IV; 1987).</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Appendix Table 1, footnotes b and d)</t>
+          <t>Shaikh &amp; Tonak 1987, Note 6, p.193</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEC-012 (No Synthetic Data Policy, 2026-05-03): ES1001 was explicitly named as one of five series with prohibited synthetic data. Remediation plan specifies: 'Extract real annual data from HDARP Table V.B (28 years available)'. Note — the registry entry references 'Table II' (labor share) while DEC-012 references 'Table V.B' (which is an Appendix III table for surplus value data). The correct source table for labor share is Chapter IV Table II (p.92). Researcher should verify which specific table the HDARP extraction covers when the relevant chunks become available.</t>
+          <t>Labor share (W/NI) is computed as the ratio of wages and salaries received by workers to national income. Tonak allocates NIPA employee compensation between labor and non-labor using an income-proportional 'labor share' factor (Total labor income / Personal income). For 1964 this factor is 0.73. The resulting series covers 1952-1980 and appears in Chapter IV, Table II ('Calculation of Labor Share, 1952-80'). The labor share is also used as the allocation key for Group II taxes and Group II expenditures throughout the dissertation.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md#DEC-012; 1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables, Chapter IV Table II, p.92); chunk_001/full_transcription.md (Abstract, Table of Contents)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Primary source: Tonak (1984) PhD Dissertation, New School for Social Research, Chapter IV Table II ('Calculation of Labor Share, 1952-80', p.92), covering 1952-1980 (28 annual observations). Underlying raw data from U.S. National Income and Product Accounts (NIPA). Table III ('Comparison of Labor Shares — Weisskopf and Tonak', p.93) provides cross-validation against Weisskopf's estimates. Per [internal-decision-record], the data_quality must be 'real_extracted' — values must be taken from HDARP-extracted Table II, not synthetically generated.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables p.v, Chapter IV Table II p.92, Table III p.93)</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>table_identification</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Labor share of national income from Tonak (1984) Chapter IV Table II, 1952-1980, 28 annual observations. Defined as total labor income / personal income; serves as allocation key throughout the dissertation's net tax framework.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>The primary table is Chapter IV Table II: 'Calculation of Labor Share, 1952-80' (p.92). A comparison table, Chapter IV Table III: 'Comparison of Labor Shares — Weisskopf and Tonak' (p.93), provides external validation. The labor share formula is also referenced in Chapter IV Table IV: 'Labor and Non-Labor Portions of Total Taxes — Selected Years' (p.95) and Table V: 'Labor and Non-Labor Portions of Total Taxes' (p.98). These tables are located in later HDARP chunks (not yet extracted in chunks 001-002).</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables pp.v-vi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Labor Share = Total labor income / Personal income. This ratio is applied to allocate Group II government expenditures and Group II personal taxes between workers and non-workers. Example value for 1964: 0.73 (cited in the 1987 Shaikh-Tonak paper's Appendix Table 1 footnote b).</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1984_Tonak_State_Revenues/chunk_001/full_transcription.md (Abstract); 1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Appendix Table 1 footnote b)</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>caveat</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Per [internal-decision-record] (No Synthetic Data Policy, 2026-05-03): ES1001 was previously identified as using synthetic data generated from summary statistics. The annual Table II values have not yet been extracted from the later HDARP chunks of Tonak (1984). Until a full HDARP extraction of Chapter IV (chunks covering pp.88-98) is completed, this series must be marked data_unavailable with an empty CSV. No np.random or benchmark-interpolation fills are permitted.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[internal-decision-log]#[internal-decision-record]</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Annual data not yet extracted — later HDARP chunks (covering pp.88-98) required</t>
+          <t>The labor share concept in Tonak (1984) is defined as wages/national income following the labor theory of value framework, which differs from conventional national accounts definitions (e.g., BLS or BEA labor share). Tonak explicitly compares with Weisskopf's estimates (Chapter IV Table III, p.93), documenting methodological divergence. Users must not conflate this series with mainstream labor share measures.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables, Chapter IV Table III p.93)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_study_note</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DEC-012 prohibits synthetic fill; series is data_unavailable until HDARP extraction completes</t>
+          <t>The 1987 Shaikh-Tonak paper uses the same labor share methodology (citing 'Tonak 1984:Chap. IV; 1987') to allocate Group II expenditures and taxes. The 1964 labor share of 0.73 is directly confirmed in S&amp;T (1987) Appendix Table 1 footnote b. The labor share for ES1001 is therefore fully consistent with the ES1101/ES1102/ES1103 series from the 1987 paper.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Appendix Table 1, footnotes b and d)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Registry entry cites 'Table II' but DEC-012 mentions 'Table V.B' — source table identity requires verification against the actual HDARP extraction</t>
+          <t>[internal-decision-record] (No Synthetic Data Policy, 2026-05-03): ES1001 was explicitly named as one of five series with prohibited synthetic data. Remediation plan specifies: 'Extract real annual data from HDARP Table V.B (28 years available)'. Note — the registry entry references 'Table II' (labor share) while [internal-decision-record] references 'Table V.B' (which is an Appendix III table for surplus value data). The correct source table for labor share is Chapter IV Table II (p.92). Researcher should verify which specific table the HDARP extraction covers when the relevant chunks become available.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[internal-decision-log]#[internal-decision-record]; 1984_Tonak_State_Revenues/chunk_002/full_transcription.md (List of Tables)</t>
         </is>
       </c>
     </row>
     <row r="17"/>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ES1002</t>
-        </is>
-      </c>
+          <t>To obtain the portions of these expenditures directed towards labor, all of the items in this group are multiplied by the "labor share" (0.73 for 1964) except the item of Transportation which is also adjusted by the "Gas Share of Passenger Cars" (Tonak 1984:Chap. IV; Appendix II).</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ES1101</t>
-        </is>
-      </c>
+          <t>Workers' share = (Total labor income / Personal income) × Group II total</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
+          <t>For rationale and procedures of "labor share method," see Tonak (1984: Chap. IV; 1987).</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Labor share of national income from Tonak (1984) Chapter IV Table II, 1952-1980, 28 annual observations. Defined as total labor income / personal income; serves as allocation key throughout the dissertation's net tax framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Annual data not yet extracted — later HDARP chunks (covering pp.88-98) required</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>[internal-decision-record] prohibits synthetic fill; series is data_unavailable until HDARP extraction completes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Registry entry cites 'Table II' but [internal-decision-record] mentions 'Table V.B' — source table identity requires verification against the actual HDARP extraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ES1002</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ES1101</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>ES1102</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
         <is>
           <t>ES1103</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
         <is>
           <t>S604</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
         <is>
           <t>S605</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Tonak_1984</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Tonak, Ertugrul Ahmet. 1984. 'A Conceptualization of State Revenues and Expenditures U.S.: 1952-1980.' PhD Dissertation, New School for Social Research. UMI Order Number 9414212.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>ST_1987</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1987. 'The Welfare State and the Myth of the Social Wage.' In Robert Cherry et al. (eds.), The Imperiled Economy, Book I. New York: Union for Radical Political Economics, pp. 184-194.</t>
         </is>
@@ -1425,7 +1606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1488,7 +1669,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1690,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1952": 34.58, "1980": 456.39}</t>
         </is>
       </c>
     </row>
@@ -1534,6 +1715,42 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>
